--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -6660,7 +6660,7 @@
         <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>96655</v>
+        <v>96658</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>93419</v>
+        <v>93422</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96658</v>
+        <v>96661</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -6660,7 +6660,7 @@
         <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>96658</v>
+        <v>96659</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>93422</v>
+        <v>93423</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96661</v>
+        <v>96662</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -6660,7 +6660,7 @@
         <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>96659</v>
+        <v>96664</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>93423</v>
+        <v>93428</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96662</v>
+        <v>96667</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -6660,7 +6660,7 @@
         <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>96664</v>
+        <v>96666</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>93428</v>
+        <v>93430</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96667</v>
+        <v>96669</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -6660,7 +6660,7 @@
         <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>96666</v>
+        <v>96672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96669</v>
+        <v>96675</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -6660,7 +6660,7 @@
         <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>96672</v>
+        <v>96674</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96675</v>
+        <v>96677</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>

--- a/artfynd/S 220-2024 artfynd.xlsx
+++ b/artfynd/S 220-2024 artfynd.xlsx
@@ -6660,7 +6660,7 @@
         <v>136443859</v>
       </c>
       <c r="B54" t="n">
-        <v>96674</v>
+        <v>96675</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>136445247</v>
       </c>
       <c r="B59" t="n">
-        <v>93434</v>
+        <v>93435</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>136443734</v>
       </c>
       <c r="B65" t="n">
-        <v>96677</v>
+        <v>96678</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>136444091</v>
       </c>
       <c r="B83" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
